--- a/assets/docs/lop3/Toan - Lop 3.xlsx
+++ b/assets/docs/lop3/Toan - Lop 3.xlsx
@@ -1455,7 +1455,7 @@
         <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Một phần mấy”, GV dùng hình động trên máy: chia một hình tròn, một băng giấy thành hai, thành bốn phần bằng nhau rồi tô màu một phần
 Năng lực số Miền 5 (Cơ bản, bậc 1): GV chiếu các hình chia phần không bằng nhau xen lẫn hình chia đúng, cho HS chọn hình đã tô một phần tư; máy báo đúng
-STEM: Trải nghiệm cùng một phần mấy (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
+STEM: Mâm cỗ Trung thu chia đều (Toán – TN&amp;XH – Công nghệ – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>STEM: Mâm cỗ Trung thu chia đều (Toán – TN&amp;XH – Công nghệ – Mĩ thuật) — dạy thay cho tiết này.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1579,7 +1583,7 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát hình động và khối 3 chiều xoay được trên màn hình, đếm đúng số mặt, cạnh, đỉnh, nêu được quan hệ giữa số đo cạnh với chu vi, diện tích.</t>
+          <t>Năng lực số 1.1 CB1b: HS quan sát hình vẽ động trên màn hình, kéo điểm M trên đoạn thẳng AB, đọc số đo AM, MB và nhận ra M là trung điểm khi AM = MB.</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1647,7 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát hình động và khối 3 chiều xoay được trên màn hình, đếm đúng số mặt, cạnh, đỉnh, nêu được quan hệ giữa số đo cạnh với chu vi, diện tích.
+          <t>Năng lực số 1.1 CB1b: HS quan sát hình vẽ động trên màn hình, kéo một điểm chạy trên đường tròn, đọc số đo bán kính, nhận ra các bán kính luôn bằng nhau và đường kính gấp 2 lần bán kính.
 KNS: KN chi tiêu hợp lí: tính toán khi mua bán, biết tiết kiệm.</t>
         </is>
       </c>
